--- a/sources/nina_step10.xlsx
+++ b/sources/nina_step10.xlsx
@@ -14084,11 +14084,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB146" t="inlineStr">
         <is>
           <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
@@ -14151,11 +14146,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB147" t="inlineStr">
         <is>
           <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
@@ -14218,11 +14208,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB148" t="inlineStr">
         <is>
           <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
@@ -14285,11 +14270,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB149" t="inlineStr">
         <is>
           <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
@@ -14352,11 +14332,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB150" t="inlineStr">
         <is>
           <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
@@ -14419,11 +14394,6 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AB151" t="inlineStr">
         <is>
           <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
@@ -14484,11 +14454,6 @@
       <c r="W152" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>TRUE</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">

--- a/sources/nina_step10.xlsx
+++ b/sources/nina_step10.xlsx
@@ -426,7 +426,7 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col hidden="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col hidden="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -9908,27 +9908,32 @@
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]</t>
+          <t>df+3,2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D]</t>
+          <t>df+3 ,2</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step]</t>
+          <t>Creeping Snake</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step]</t>
+          <t>Creeping Snake</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1 1 0</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10020,7 +10025,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D] &lt;4</t>
+          <t>df+3 ,2 &lt;4</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10030,12 +10035,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Roundhouse</t>
+          <t>Creeping Snake – Roundhouse</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1 1 0 1</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -10122,7 +10127,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],d+3</t>
+          <t>df+3 ,2 ,d+3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -10132,7 +10137,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Low Spin Kick</t>
+          <t>Creeping Snake – Low Spin Kick</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -10229,7 +10234,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],d+3 ,2</t>
+          <t>df+3 ,2 ,d+3 ,2</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10239,7 +10244,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Low Spin Kick – Upper</t>
+          <t>Creeping Snake – Low Spin Kick – Upper</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -10341,7 +10346,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],d+3 ,4</t>
+          <t>df+3 ,2 ,d+3 ,4</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -10351,7 +10356,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Low Spin Kick – High Kick</t>
+          <t>Creeping Snake – Low Spin Kick – High Kick</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10443,7 +10448,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],3 ,3</t>
+          <t>df+3 ,2 ,3 ,3</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -10453,7 +10458,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo</t>
+          <t>Creeping Snake – Spike Combo</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10545,7 +10550,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],3 ,3 ,2</t>
+          <t>df+3 ,2 ,3 ,3 ,2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -10555,7 +10560,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo – Upper</t>
+          <t>Creeping Snake – Spike Combo – Upper</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10657,7 +10662,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],3 ,3 ,4</t>
+          <t>df+3 ,2 ,3 ,3 ,4</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10667,7 +10672,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo – High Kick</t>
+          <t>Creeping Snake – Spike Combo – High Kick</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10759,7 +10764,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],3 ,3 ,d+4</t>
+          <t>df+3 ,2 ,3 ,3 ,d+4</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10769,7 +10774,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Spike Combo – Shin Kick</t>
+          <t>Creeping Snake – Spike Combo – Shin Kick</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -10861,7 +10866,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],3 &lt;4</t>
+          <t>df+3 ,2 ,3 &lt;4</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -10871,7 +10876,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Head Ringer</t>
+          <t>Creeping Snake – Head Ringer</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10963,7 +10968,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>df+3 ,2 [~U_~D],1 &lt;4</t>
+          <t>df+3 ,2 ,1 &lt;4</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -10973,7 +10978,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Creeping Snake [Side Step] – Biting Snake</t>
+          <t>Creeping Snake – Biting Snake</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12391,32 +12396,37 @@
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t>FC+4,1 [~U_~D]</t>
+          <t>FC+4,1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FC+4 ,1 [~U_~D]</t>
+          <t>FC+4 ,1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>d+4,1 [~U_~D]</t>
+          <t>d+4,1</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [Side Step]</t>
+          <t>Shin Kick - Spin Punch</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [Side Step]</t>
+          <t>Shin Kick - Spin Punch</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>1 1 0</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">

--- a/sources/nina_step10.xlsx
+++ b/sources/nina_step10.xlsx
@@ -965,6 +965,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>579379b9-32f7-4d30-8142-6af0377daf6b</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>579379b9-32f7-4d30-8142-6af0377daf6b</t>
@@ -1037,6 +1042,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>d3ced517-a634-43fa-a3ef-26274a6c6294</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>d3ced517-a634-43fa-a3ef-26274a6c6294</t>
@@ -1102,6 +1112,11 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>75937ef0-ab7d-422f-82fa-406485f60d4e</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -14037,6 +14052,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
+        </is>
+      </c>
       <c r="AB145" t="inlineStr">
         <is>
           <t>90a39103-ed06-4b93-9933-d1bc034dbdd8</t>
@@ -14094,6 +14114,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
+        </is>
+      </c>
       <c r="AB146" t="inlineStr">
         <is>
           <t>9dc8fd41-1e0f-44c0-a345-f0f349baec9e</t>
@@ -14156,6 +14181,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
+        </is>
+      </c>
       <c r="AB147" t="inlineStr">
         <is>
           <t>af662811-0ddd-49dd-b491-d67dcf8cfe25</t>
@@ -14218,6 +14248,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
+        </is>
+      </c>
       <c r="AB148" t="inlineStr">
         <is>
           <t>680e22f1-9e4f-4d94-a1d4-ec6dfccc07b2</t>
@@ -14280,6 +14315,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
+        </is>
+      </c>
       <c r="AB149" t="inlineStr">
         <is>
           <t>27611fec-35c5-434c-a334-41f883b8a9e2</t>
@@ -14342,6 +14382,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
+        </is>
+      </c>
       <c r="AB150" t="inlineStr">
         <is>
           <t>c46f7713-a26a-46bf-b90c-9659050c65df</t>
@@ -14404,6 +14449,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
+        </is>
+      </c>
       <c r="AB151" t="inlineStr">
         <is>
           <t>4d785cdc-7ffa-496f-b320-1a11e22d242b</t>
@@ -14466,6 +14516,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>6c5e4b4b-1493-459e-bc6c-bb7d303d3d8c</t>
+        </is>
+      </c>
       <c r="AB152" t="inlineStr">
         <is>
           <t>6c5e4b4b-1493-459e-bc6c-bb7d303d3d8c</t>
@@ -14533,6 +14588,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
+        </is>
+      </c>
       <c r="AB153" t="inlineStr">
         <is>
           <t>f619683e-d12b-4f0c-9a23-a82c66d6108f</t>
@@ -14595,6 +14655,11 @@
           <t>Initial throw does no damage when doing the Shoulder Buster.</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
+        </is>
+      </c>
       <c r="AB154" t="inlineStr">
         <is>
           <t>f803c5d5-9bf2-4004-b5d9-e78fbc8254b1</t>
@@ -14657,6 +14722,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>b05111d7-0489-49ed-a291-0f34f0e03355</t>
+        </is>
+      </c>
       <c r="AB155" t="inlineStr">
         <is>
           <t>b05111d7-0489-49ed-a291-0f34f0e03355</t>
@@ -14729,6 +14799,11 @@
           <t>CH</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
+        </is>
+      </c>
       <c r="AB156" t="inlineStr">
         <is>
           <t>49d8679e-156a-4cf1-bc63-eb8c85f2570d</t>
@@ -14786,6 +14861,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>4bf63cb5-b99b-4c63-985e-8f513100ba2e</t>
+        </is>
+      </c>
       <c r="AB157" t="inlineStr">
         <is>
           <t>4bf63cb5-b99b-4c63-985e-8f513100ba2e</t>
@@ -14848,6 +14928,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>42ce7230-87bf-452a-b714-833a0716e519</t>
+        </is>
+      </c>
       <c r="AB158" t="inlineStr">
         <is>
           <t>42ce7230-87bf-452a-b714-833a0716e519</t>
@@ -14915,6 +15000,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
+        </is>
+      </c>
       <c r="AB159" t="inlineStr">
         <is>
           <t>8a0f95c3-6e08-462b-bd73-537af35aebfb</t>
@@ -14972,6 +15062,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>a1b4f0ce-7fdd-4e52-a960-300cccac0677</t>
+        </is>
+      </c>
       <c r="AB160" t="inlineStr">
         <is>
           <t>a1b4f0ce-7fdd-4e52-a960-300cccac0677</t>
@@ -15034,6 +15129,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
+        </is>
+      </c>
       <c r="AB161" t="inlineStr">
         <is>
           <t>cd43d6c3-45f7-4ef1-a13a-d4147535222f</t>
@@ -15096,6 +15196,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>ff6b8176-7993-4f56-a26f-4accb79a4869</t>
+        </is>
+      </c>
       <c r="AB162" t="inlineStr">
         <is>
           <t>ff6b8176-7993-4f56-a26f-4accb79a4869</t>
@@ -15158,6 +15263,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>f956b41d-482e-44be-a215-575d5455d551</t>
+        </is>
+      </c>
       <c r="AB163" t="inlineStr">
         <is>
           <t>f956b41d-482e-44be-a215-575d5455d551</t>
@@ -15220,6 +15330,11 @@
           <t>Front</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>55a9a5db-779c-4431-878f-621fd1035127</t>
+        </is>
+      </c>
       <c r="AB164" t="inlineStr">
         <is>
           <t>55a9a5db-779c-4431-878f-621fd1035127</t>
@@ -15277,6 +15392,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
+        </is>
+      </c>
       <c r="AB165" t="inlineStr">
         <is>
           <t>c5659aeb-e8d4-4009-856a-cabcba3a3f3a</t>
@@ -15339,6 +15459,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>db158e94-71bc-4b8f-8400-62ab50e6d071</t>
+        </is>
+      </c>
       <c r="AB166" t="inlineStr">
         <is>
           <t>db158e94-71bc-4b8f-8400-62ab50e6d071</t>
@@ -15401,6 +15526,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>8b0ad6c8-da48-4887-ace2-9a1997cd7b4e</t>
+        </is>
+      </c>
       <c r="AB167" t="inlineStr">
         <is>
           <t>8b0ad6c8-da48-4887-ace2-9a1997cd7b4e</t>
@@ -15463,6 +15593,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>55349cf9-9743-4042-9932-3196803d0f29</t>
+        </is>
+      </c>
       <c r="AB168" t="inlineStr">
         <is>
           <t>55349cf9-9743-4042-9932-3196803d0f29</t>
@@ -15525,6 +15660,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>5b751088-f08a-4dd7-ae97-ae70ef70c091</t>
+        </is>
+      </c>
       <c r="AB169" t="inlineStr">
         <is>
           <t>5b751088-f08a-4dd7-ae97-ae70ef70c091</t>
@@ -15585,6 +15725,11 @@
       <c r="W170" t="inlineStr">
         <is>
           <t>1+2</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>4d4ecd62-8ffe-41f7-b612-20d6890a6862</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
@@ -15804,6 +15949,11 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>3a2ee9ee-dce4-4c78-9f09-568b5f25c2e2</t>
+        </is>
+      </c>
       <c r="AB174" t="inlineStr">
         <is>
           <t>3a2ee9ee-dce4-4c78-9f09-568b5f25c2e2</t>
@@ -15856,6 +16006,11 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>d1a1e5da-c800-416e-b406-c97d2d8c4a46</t>
+        </is>
+      </c>
       <c r="AB175" t="inlineStr">
         <is>
           <t>d1a1e5da-c800-416e-b406-c97d2d8c4a46</t>
@@ -15908,6 +16063,11 @@
           <t>hhhhhllmlm</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>9ad750c5-c557-44a5-a567-b12660f9b35b</t>
+        </is>
+      </c>
       <c r="AB176" t="inlineStr">
         <is>
           <t>9ad750c5-c557-44a5-a567-b12660f9b35b</t>
@@ -15960,6 +16120,11 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>995c552e-236a-4223-8cec-5e2855a523ed</t>
+        </is>
+      </c>
       <c r="AB177" t="inlineStr">
         <is>
           <t>995c552e-236a-4223-8cec-5e2855a523ed</t>
@@ -16012,6 +16177,11 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>5b9889d2-e50a-4a76-ac9e-6eda0614e269</t>
+        </is>
+      </c>
       <c r="AB178" t="inlineStr">
         <is>
           <t>5b9889d2-e50a-4a76-ac9e-6eda0614e269</t>
@@ -16064,6 +16234,11 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>ee2aac21-2026-4147-a965-2b667009bfd7</t>
+        </is>
+      </c>
       <c r="AB179" t="inlineStr">
         <is>
           <t>ee2aac21-2026-4147-a965-2b667009bfd7</t>
@@ -16116,6 +16291,11 @@
           <t>mhhhhlhhhh</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>60f598e7-610a-4bd3-9571-e439caa72bf2</t>
+        </is>
+      </c>
       <c r="AB180" t="inlineStr">
         <is>
           <t>60f598e7-610a-4bd3-9571-e439caa72bf2</t>
@@ -16168,6 +16348,11 @@
           <t>mhhhhlhhlm</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>560bc65a-15b1-4d87-9eb5-e20bb762dfc6</t>
+        </is>
+      </c>
       <c r="AB181" t="inlineStr">
         <is>
           <t>560bc65a-15b1-4d87-9eb5-e20bb762dfc6</t>
@@ -16220,6 +16405,11 @@
           <t>mhhhhllmlm</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>3ca0e736-a79e-4350-8dab-e3dc2112e74b</t>
+        </is>
+      </c>
       <c r="AB182" t="inlineStr">
         <is>
           <t>3ca0e736-a79e-4350-8dab-e3dc2112e74b</t>
@@ -16282,6 +16472,11 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>f37af239-8d33-4787-93e6-4352245294b9</t>
+        </is>
+      </c>
       <c r="AB183" t="inlineStr">
         <is>
           <t>f37af239-8d33-4787-93e6-4352245294b9</t>
@@ -16344,6 +16539,11 @@
           <t>hhhhhlhhlm</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>fce87066-f49e-4f90-b59c-e0dfac99082f</t>
+        </is>
+      </c>
       <c r="AB184" t="inlineStr">
         <is>
           <t>fce87066-f49e-4f90-b59c-e0dfac99082f</t>
@@ -16404,6 +16604,11 @@
       <c r="U185" t="inlineStr">
         <is>
           <t>hhhhhllmlm</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>d4f56864-b1c5-4ee6-a66e-c349919b767a</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
